--- a/output/pdf_financials_xlsx/GSP.xlsx
+++ b/output/pdf_financials_xlsx/GSP.xlsx
@@ -1038,46 +1038,46 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.026153</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.023378</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.004914</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000695</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.001073</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.005878</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.004142</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.011327</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.006552</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.00553</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.001259</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.008161</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.001381</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.000308</v>
       </c>
     </row>
     <row r="13">
@@ -2034,46 +2034,46 @@
         <v>0.964486</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.071628</v>
+        <v>-4.097781</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.293084</v>
+        <v>-2.316462</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.082313</v>
+        <v>-2.087227</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.261314</v>
+        <v>-1.262009</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.072156</v>
+        <v>-1.073229</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.951483</v>
+        <v>-2.957361</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-3.164368</v>
+        <v>-3.16851</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-3.148598</v>
+        <v>-3.159925</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.724723</v>
+        <v>-2.731275</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-4.87822</v>
+        <v>-4.88375</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-2.491863</v>
+        <v>-2.493122</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-6.583234</v>
+        <v>-6.591395</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.89504</v>
+        <v>-2.896421</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-2.32678</v>
+        <v>-2.327088</v>
       </c>
     </row>
     <row r="28">
@@ -2150,46 +2150,46 @@
         <v>0.964486</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.071628</v>
+        <v>-4.097781</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.293084</v>
+        <v>-2.316462</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.053351</v>
+        <v>-2.058265</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.236048</v>
+        <v>-1.236743</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.066008</v>
+        <v>-1.067081</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.945685</v>
+        <v>-2.951563</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.159149</v>
+        <v>-3.163291</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-3.148598</v>
+        <v>-3.159925</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.724723</v>
+        <v>-2.731275</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-4.87822</v>
+        <v>-4.88375</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-2.491863</v>
+        <v>-2.493122</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-6.583234</v>
+        <v>-6.591395</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.89504</v>
+        <v>-2.896421</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-2.32678</v>
+        <v>-2.327088</v>
       </c>
     </row>
     <row r="30">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>16224.32838179519</v>
+        <v>16263.15581542351</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-177848.6330935252</v>
+        <v>-177948.6330935252</v>
       </c>
       <c r="I30" s="1" t="inlineStr">
         <is>
@@ -2440,55 +2440,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.381816</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.003243</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.003243</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.954322</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.259103</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.18153</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.575841</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.781257</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.957093</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.464905</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.975158</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>7.490488</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.712079</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.337831</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.409488</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.063343</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.029224</v>
       </c>
     </row>
     <row r="35">
@@ -2556,55 +2556,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.381816</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.003243</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.003243</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.954322</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.259103</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.18153</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.575841</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.781257</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.957093</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.464905</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.975158</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>7.490488</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.712079</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.337831</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.409488</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.063343</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.029224</v>
       </c>
     </row>
     <row r="37">
@@ -3252,55 +3252,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>4.340133</v>
+        <v>1.958317</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.524952</v>
+        <v>0.521709</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.524952</v>
+        <v>0.521709</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.992892</v>
+        <v>0.03857</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.272955</v>
+        <v>0.013852</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.208892</v>
+        <v>0.027362</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.593822</v>
+        <v>0.017981</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.859935</v>
+        <v>0.078678</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.045267</v>
+        <v>0.088174</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.646029</v>
+        <v>0.181124</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.008112</v>
+        <v>0.032954</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>7.500622</v>
+        <v>0.010134</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.02798</v>
+        <v>0.315901</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.420604</v>
+        <v>0.082773</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.476632</v>
+        <v>0.067144</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.12345</v>
+        <v>0.060107</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.07231</v>
+        <v>0.043086</v>
       </c>
     </row>
     <row r="49">
@@ -9047,7 +9047,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -17451,7 +17451,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -20014,7 +20014,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
@@ -35168,7 +35168,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -36443,7 +36443,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -41106,7 +41106,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -41708,7 +41708,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -43716,7 +43716,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -44207,7 +44207,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E356" s="5" t="n">

--- a/output/pdf_financials_xlsx/GSP.xlsx
+++ b/output/pdf_financials_xlsx/GSP.xlsx
@@ -7185,7 +7185,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.002047</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
@@ -7737,16 +7737,16 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0</v>
+        <v>1.098908</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0</v>
+        <v>1.748383</v>
       </c>
       <c r="F120" s="3" t="n">
         <v>0</v>
@@ -23125,7 +23125,11 @@
           <t>Proceeds from the disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -28307,7 +28311,11 @@
           <t>Issue of common shares, net of issue costs</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -33608,7 +33616,11 @@
           <t>Issuance of common shares, net of issue costs</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E249" s="5" t="n">
         <v>0.016</v>
       </c>

--- a/output/pdf_financials_xlsx/GSP.xlsx
+++ b/output/pdf_financials_xlsx/GSP.xlsx
@@ -7377,22 +7377,22 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.981396</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>1.182412</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>2.150539</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>1.668385</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>1.555556</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.081441</v>
       </c>
       <c r="H115" s="3" t="n">
         <v>0</v>
@@ -26891,7 +26891,11 @@
           <t>Proceeds from the sale of investments</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -31640,7 +31644,11 @@
           <t>Proceeds from the sale of investments</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E229" s="5" t="n">
         <v>0.981396</v>
       </c>
@@ -33420,7 +33428,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E247" s="5" t="n">
         <v>-0.418364</v>
       </c>
